--- a/excel/锌.xlsx
+++ b/excel/锌.xlsx
@@ -495,7 +495,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AE44"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -4001,7 +4001,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Z16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -4384,6 +4384,11 @@
         <f>IF(AND(ISNUMBER(V4),ISNUMBER(O4),O4&lt;&gt;0),(V4-O4)/O4,"-")</f>
         <v/>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Q2 2026财报已发布（Revenue 6.37T KRW/OP 587B KRW），精炼锌产量数据待补充</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4452,13 +4457,16 @@
         <f>IF(AND(ISNUMBER(T5),ISNUMBER(N5),N5&lt;&gt;0),(T5-N5)/N5,"-")</f>
         <v/>
       </c>
+      <c r="V5" t="n">
+        <v>22.09</v>
+      </c>
       <c r="W5">
         <f>IF(AND(ISNUMBER(V5),ISNUMBER(O5),O5&lt;&gt;0),(V5-O5)/O5,"-")</f>
         <v/>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>品位和采选顺序如期上升</t>
+          <t>26Q2锌22.09万吨(-6.2%): 运营中断和电力限制；来自Glencore 2026-H1 Report(PDF, 2026-07-29)</t>
         </is>
       </c>
     </row>
@@ -4618,6 +4626,11 @@
           <t>氧化锌产出增加</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>26Q2 Nexa冶炼锌金属+氧化合计125kt(-10%)；分冶炼厂数据未单独披露，待补充</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4695,6 +4708,11 @@
           <t>产量恢复</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>26Q2 Nexa冶炼锌金属+氧化合计125kt(-10%)；分冶炼厂数据未单独披露，待补充</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4847,6 +4865,16 @@
         <f>IF(AND(ISNUMBER(V10),ISNUMBER(O10),O10&lt;&gt;0),(V10-O10)/O10,"-")</f>
         <v/>
       </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Q2 2026财报已发布，分冶炼厂产量数据待补充</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>26Q2 Nexa冶炼锌金属+氧化合计125kt(-10%)；分冶炼厂数据未单独披露，待补充</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4922,6 +4950,11 @@
       <c r="X11" t="inlineStr">
         <is>
           <t>KZ产能分配至SMC</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>26Q2 Nexa冶炼锌金属+氧化合计125kt(-10%)；分冶炼厂数据未单独披露，待补充</t>
         </is>
       </c>
     </row>
@@ -5338,8 +5371,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
@@ -5516,7 +5549,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26Q1: 71.7</t>
+          <t>26Q2: 92.2（H1累计164.0；iFinD购建固定资产/无形资产支付现金）</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5563,7 +5596,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>—（港股无季报现金流）</t>
+          <t>26H1: 553.8（iFinD 20260630 purchase_of_ppe_and_ia_oas=553.8M USD；无Q1单季数据）</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5866,6 +5899,13 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>官网人工</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>注：绿色=iFinD现金流量表自动抓取（季度可更新）；橙色=公司官网财报人工核实（财年口径各异：Vedanta/HZL止3月、South32止6月）。各家资本开支口径不同（净额/总额/增长性），横向比较请注意。Polymetal已私有化，无公开数据。</t>
         </is>
       </c>
     </row>
@@ -5880,8 +5920,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="80" customWidth="1" min="2" max="2"/>
@@ -6228,6 +6268,74 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Nexa、Korea Zinc Q2 2026财报已发布：Nexa于8/5盘后发布Q2 2026（Net Income $98M/Adj EBITDA $286M），Korea Zinc于8/5发布Q2 2026（Revenue 6.37T KRW/OP 587B KRW/Net Profit 351.5B KRW）。但详细分矿山/冶炼厂产量数据及资本开支暂未在公开渠道获取，26Q2列留空待补充；Mitsui Mining预计8/7发布。其余企业（Vedanta、Teck、Glencore、Boliden、MMG、Newmont、South32、Ivanhoe）Q2数据均已在此前更新。</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Nexa IR(ri.nexaresources.com, 2026-08-05)/Korea Zinc earnings news(Yonhap/RTTNews, 2026-08-05)/Yahoo Finance NEXA quarterly cashflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>补入Nexa 26Q2 iFinD现金流量表数据：H1资本开支164.0百万USD（Q1=71.7, Q2=92.2）；Nexa合并矿山锌产量79kt(+8%)、合并冶炼锌金属+氧化125kt(-10%)已在财报中披露，但分矿山/分冶炼厂产量数据未单独披露，锌矿表和冶炼表备注已更新。其余企业（Korea Zinc、Mitsui Mining、Glencore冶炼厂、Nyrstar）Q2详细产量数据在公开渠道仍无法获取。</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>iFinD现金流量表（NEXA.N 20260630: purchase_of_ppe_and_ia_oas=163.988）/ Nexa Q2 2026财报及Nexa Peru财报</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>补入Glencore冶炼26Q2产量22.09万吨(同比-6.2%，来自Glencore 2026-H1 Report)；补入MMG(1208.HK) 26H1资本开支553.8百万USD（iFinD现金流量表20260630首次入库，无Q1单季数据）。其余企业Q2详细产量/资本开支数据在公开渠道仍无法获取：Korea Zinc分冶炼厂、Mitsui Mining、Nexa分冶炼厂、Nyrstar。</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Glencore 2026-H1 Report(PDF, 2026-07-29)/iFinD现金流量表（1208.HK 20260630）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>事故恢复（第4次）：真库被旧内存副本覆盖保存，锌矿表回退到 08-18 版式统一前、丢失 07-29 新增的 16 家公司行与 08-18 的 7 家骨架行（紫金矿业/Fresnillo 等），致 caibao-hub 构建 3 条核对 FAIL（锌矿总计26Q1/紫金25总计/Fresnillo 26Q2）。以 excel/锌.xlsx（08-18 统一版式完整态）为基线，并回真库 08-06(Nexa/Korea Zinc财报)/08-12(Nexa资本开支)/08-21(Glencore冶炼26Q2+MMG 26H1资本开支) 三笔更新后恢复。</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>excel/锌.xlsx 与真库逐格对比（2026-08-21）；备份见 caibao-hub/backup_20260821/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel/锌.xlsx
+++ b/excel/锌.xlsx
@@ -494,8 +494,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE44"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:AE47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -1478,19 +1478,22 @@
         <v/>
       </c>
       <c r="T10" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="U10">
         <f>IF(AND(ISNUMBER(T10),ISNUMBER(N10),N10&lt;&gt;0),(T10-N10)/N10,"-")</f>
         <v/>
       </c>
+      <c r="V10" t="n">
+        <v>2.19</v>
+      </c>
       <c r="W10">
         <f>IF(AND(ISNUMBER(V10),ISNUMBER(O10),O10&lt;&gt;0),(V10-O10)/O10,"-")</f>
         <v/>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>白银刺激</t>
+          <t>2Q26：品位升至1.64%+block caving投产，产量同比-6.1%</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1565,19 +1568,22 @@
         <v/>
       </c>
       <c r="T11" t="n">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="U11">
         <f>IF(AND(ISNUMBER(T11),ISNUMBER(N11),N11&lt;&gt;0),(T11-N11)/N11,"-")</f>
         <v/>
       </c>
+      <c r="V11" t="n">
+        <v>3.26</v>
+      </c>
       <c r="W11">
         <f>IF(AND(ISNUMBER(V11),ISNUMBER(O11),O11&lt;&gt;0),(V11-O11)/O11,"-")</f>
         <v/>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>运营平稳</t>
+          <t>2Q26：同比+18.8%，运营改善</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -3919,74 +3925,197 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>NEXA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>秘鲁</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>El Porvenir</t>
+        </is>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44">
+        <f>IF(AND(ISNUMBER(T44),ISNUMBER(N44),N44&lt;&gt;0),(T44-N44)/N44,"-")</f>
+        <v/>
+      </c>
+      <c r="V44" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W44">
+        <f>IF(AND(ISNUMBER(V44),ISNUMBER(P44),P44&lt;&gt;0),(V44-P44)/P44,"-")</f>
+        <v/>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>2Q26：同比-3.7%，Q1扰动后恢复</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>来源：Nexa 2Q26 Production Report（SEC EDGAR 6-K ex99-1，2026-08-05）；2026-08-23 补录</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>NEXA</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>秘鲁</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Atacocha</t>
+        </is>
+      </c>
+      <c r="T45" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="U45">
+        <f>IF(AND(ISNUMBER(T45),ISNUMBER(N45),N45&lt;&gt;0),(T45-N45)/N45,"-")</f>
+        <v/>
+      </c>
+      <c r="V45" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W45">
+        <f>IF(AND(ISNUMBER(V45),ISNUMBER(P45),P45&lt;&gt;0),(V45-P45)/P45,"-")</f>
+        <v/>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>2Q26：同比-4.2%</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>来源：Nexa 2Q26 Production Report（SEC EDGAR 6-K ex99-1，2026-08-05）；2026-08-23 补录</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>NEXA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>巴西</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Aripuanã</t>
+        </is>
+      </c>
+      <c r="T46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U46">
+        <f>IF(AND(ISNUMBER(T46),ISNUMBER(N46),N46&lt;&gt;0),(T46-N46)/N46,"-")</f>
+        <v/>
+      </c>
+      <c r="V46" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="W46">
+        <f>IF(AND(ISNUMBER(V46),ISNUMBER(P46),P46&lt;&gt;0),(V46-P46)/P46,"-")</f>
+        <v/>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>2Q26：同比+43.8%；Q1创纪录13kt，Q2尾矿过滤机投产过渡季</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>来源：Nexa 2Q26 Production Report（SEC EDGAR 6-K ex99-1，2026-08-05）；2026-08-23 补录</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>总计</t>
         </is>
       </c>
-      <c r="D44">
-        <f>SUM(D2:D43)</f>
-        <v/>
-      </c>
-      <c r="E44">
-        <f>SUM(E2:E43)</f>
-        <v/>
-      </c>
-      <c r="F44">
-        <f>SUM(F2:F43)</f>
-        <v/>
-      </c>
-      <c r="G44">
-        <f>SUM(G2:G43)</f>
-        <v/>
-      </c>
-      <c r="H44">
-        <f>SUM(H2:H43)</f>
-        <v/>
-      </c>
-      <c r="I44">
-        <f>SUM(I2:I43)</f>
-        <v/>
-      </c>
-      <c r="J44">
-        <f>SUM(J2:J43)</f>
-        <v/>
-      </c>
-      <c r="K44">
-        <f>SUM(K2:K43)</f>
-        <v/>
-      </c>
-      <c r="L44">
-        <f>SUM(L2:L43)</f>
-        <v/>
-      </c>
-      <c r="M44">
-        <f>SUM(M2:M43)</f>
-        <v/>
-      </c>
-      <c r="N44">
-        <f>SUM(N2:N43)</f>
-        <v/>
-      </c>
-      <c r="O44">
-        <f>SUM(O2:O43)</f>
-        <v/>
-      </c>
-      <c r="P44">
-        <f>SUM(P2:P43)</f>
-        <v/>
-      </c>
-      <c r="Q44">
-        <f>SUM(Q2:Q43)</f>
-        <v/>
-      </c>
-      <c r="R44">
-        <f>SUM(R2:R43)</f>
-        <v/>
-      </c>
-      <c r="T44" t="n">
-        <v>143.3153</v>
-      </c>
-      <c r="V44" t="n">
-        <v>101.3142</v>
+      <c r="D47">
+        <f>SUM(D2:D46)</f>
+        <v/>
+      </c>
+      <c r="E47">
+        <f>SUM(E2:E46)</f>
+        <v/>
+      </c>
+      <c r="F47">
+        <f>SUM(F2:F46)</f>
+        <v/>
+      </c>
+      <c r="G47">
+        <f>SUM(G2:G46)</f>
+        <v/>
+      </c>
+      <c r="H47">
+        <f>SUM(H2:H46)</f>
+        <v/>
+      </c>
+      <c r="I47">
+        <f>SUM(I2:I46)</f>
+        <v/>
+      </c>
+      <c r="J47">
+        <f>SUM(J2:J46)</f>
+        <v/>
+      </c>
+      <c r="K47">
+        <f>SUM(K2:K46)</f>
+        <v/>
+      </c>
+      <c r="L47">
+        <f>SUM(L2:L46)</f>
+        <v/>
+      </c>
+      <c r="M47">
+        <f>SUM(M2:M46)</f>
+        <v/>
+      </c>
+      <c r="N47">
+        <f>SUM(N2:N46)</f>
+        <v/>
+      </c>
+      <c r="O47">
+        <f>SUM(O2:O46)</f>
+        <v/>
+      </c>
+      <c r="P47">
+        <f>SUM(P2:P46)</f>
+        <v/>
+      </c>
+      <c r="Q47">
+        <f>SUM(Q2:Q46)</f>
+        <v/>
+      </c>
+      <c r="R47">
+        <f>SUM(R2:R46)</f>
+        <v/>
+      </c>
+      <c r="T47" t="n">
+        <v>145.8053</v>
+      </c>
+      <c r="V47" t="n">
+        <v>109.2542</v>
       </c>
     </row>
   </sheetData>
@@ -4001,7 +4130,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Z16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -5372,7 +5501,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
@@ -5902,6 +6031,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -5920,8 +6050,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="80" customWidth="1" min="2" max="2"/>
@@ -6336,6 +6466,23 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Nexa 2Q26 分矿产量入库：Cerro Lindo 2.16/2.19、Vazante 3.26/3.26（修正Q1）+ 新增 El Porvenir/Atacocha/Aripuanã 三行；NEXA 26Q2 锌合计 7.93 万吨（+7.9%）；总计行 SUM 范围已扩</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SEC EDGAR 6-K ex99-1（2026-08-05）sec.gov/Archives/edgar/data/1713930/000129281426004059/ex99-1.htm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel/锌.xlsx
+++ b/excel/锌.xlsx
@@ -2625,13 +2625,16 @@
         <f>IF(AND(ISNUMBER(T24),ISNUMBER(N24),N24&lt;&gt;0),(T24-N24)/N24,"-")</f>
         <v/>
       </c>
+      <c r="V24" t="n">
+        <v>6.8718</v>
+      </c>
       <c r="W24">
         <f>IF(AND(ISNUMBER(V24),ISNUMBER(O24),O24&lt;&gt;0),(V24-O24)/O24,"-")</f>
         <v/>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>官方Informe del Director口径（含Juanicipio 100%应付产量，非权益）；25年下滑因Tizapa罢工（25年6月底复产），26Q1同比+15.6%；26Q2约8月初披露</t>
+          <t>官方Informe del Director 2T26口径(含Fresnillo 74.99%+Juanicipio 100%应付，非权益)；26Q2=6.8718万吨(68,718吨)同比+14.2%(主因Tizapa复产)/环比+3.1%。来源:penoles.com.mx Informe_Director_2T26_Eng.pdf(2026-08-04)</t>
         </is>
       </c>
     </row>
@@ -2912,13 +2915,18 @@
         <f>IF(AND(ISNUMBER(T29),ISNUMBER(N29),N29&lt;&gt;0),(T29-N29)/N29,"-")</f>
         <v/>
       </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>待发布</t>
+        </is>
+      </c>
       <c r="W29">
         <f>IF(AND(ISNUMBER(V29),ISNUMBER(O29),O29&lt;&gt;0),(V29-O29)/O29,"-")</f>
         <v/>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>官方Operating Update应付锌(payable)口径，季度取整至千吨；26Q1同比-19%（超常降雨+计划检修）；Century近服务年限末期；26Q2不单发（H1业绩约8月下旬）</t>
+          <t>Sibanye H1 2026（JSE，约 8/28）待发布；FY2025 Century 应付锌 101kt（+22% 超指引上限 97.8kt）。源：Sibanye 2025 年报（2/20）</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -2969,13 +2977,16 @@
         <f>IF(AND(ISNUMBER(T30),ISNUMBER(N30),N30&lt;&gt;0),(T30-N30)/N30,"-")</f>
         <v/>
       </c>
+      <c r="V30" t="n">
+        <v>1.13</v>
+      </c>
       <c r="W30">
         <f>IF(AND(ISNUMBER(V30),ISNUMBER(O30),O30&lt;&gt;0),(V30-O30)/O30,"-")</f>
         <v/>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>官方Production Report精矿应付锌(payable)口径；25Q4环比+40%（East Region品位改善）；26Q1降因Nikolayevsky选厂1月计划检修；26Q2未发布（约8月）</t>
+          <t>26Q2 精矿含锌 11.3kt=1.13 万吨（+9% QoQ，处理量提升）；H1 21.7kt（+6%，品位改善）。源：KAZ Q2 2026 生产报告（8/11，SMM 快讯）</t>
         </is>
       </c>
     </row>
@@ -3015,19 +3026,22 @@
         <v/>
       </c>
       <c r="T31" t="n">
-        <v>1.52</v>
+        <v>1.26</v>
       </c>
       <c r="U31">
         <f>IF(AND(ISNUMBER(T31),ISNUMBER(N31),N31&lt;&gt;0),(T31-N31)/N31,"-")</f>
         <v/>
       </c>
+      <c r="V31" t="n">
+        <v>1.56</v>
+      </c>
       <c r="W31">
         <f>IF(AND(ISNUMBER(V31),ISNUMBER(O31),O31&lt;&gt;0),(V31-O31)/O31,"-")</f>
         <v/>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>官方权益(attributable)口径；25年9月起并计Juanicipio 44%权益（收购MAG）；25Q3为全年推算值；2025年5.59万吨超原指引4.2-4.5；26Q2业绩8/12发布</t>
+          <t>26Q2 锌产量 15.6kt=1.56 万吨（Q1 12.6kt）；权益口径。源：Pan American Silver Q2 2026（8/12）</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -3138,13 +3152,18 @@
         <f>IF(AND(ISNUMBER(T33),ISNUMBER(N33),N33&lt;&gt;0),(T33-N33)/N33,"-")</f>
         <v/>
       </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>已发布待拆</t>
+        </is>
+      </c>
       <c r="W33">
         <f>IF(AND(ISNUMBER(V33),ISNUMBER(O33),O33&lt;&gt;0),(V33-O33)/O33,"-")</f>
         <v/>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2025-09-03并入DPM Metals；25Q1/Q2为Adriatic官方应付精矿含锌口径；25Q3/Q4/25Y为券商跟踪表口径(2026-07)待官方核实（与Q1/Q2官方值口径不一致）；26Q1为DPM官方精矿含锌10.0Mlbs≈0.45万吨（口径不同）；Vares爬产，26Q2分金属数据7/30发布</t>
+          <t>DPM Metals Q2 2026（7/30）已发，Vareš 宣布商产、年底满产；锌分矿明细待拆 → 暂记。源：dpmmetals.com 7/30</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3423,10 +3442,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O39" t="n">
+        <v>0.2359</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -3451,18 +3468,21 @@
         <f>IF(AND(ISNUMBER(T39),ISNUMBER(N39),N39&lt;&gt;0),(T39-N39)/N39,"-")</f>
         <v/>
       </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V39" t="n">
+        <v>0.1996</v>
       </c>
       <c r="W39">
         <f>IF(AND(ISNUMBER(V39),ISNUMBER(O39),O39&lt;&gt;0),(V39-O39)/O39,"-")</f>
         <v/>
       </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>26Q2(FY27Q1,止6/30)锌 4.4Mlb=1,996吨=0.20万吨(同比-15%)：6月中主动停产安全整改+回采品位下降；Ying 1.6Mlb+GC 2.9Mlb</t>
+        </is>
+      </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>锌精矿含锌量；财年止3月（FY Q4=自然Q1）；季报（TSX/NYSE）；铅目录同步建行；2026-08-18新增骨架行，数据待回填</t>
+          <t>锌精矿含锌量；财年止3月（FY Q4=自然Q1）；季报（TSX/NYSE）；铅目录同步建行；2026-08-18新增骨架行，数据待回填；源：Silvercorp 6-K 2026-07-15（SEC）；磅×0.0004536=吨</t>
         </is>
       </c>
     </row>
@@ -3537,10 +3557,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O40" t="n">
+        <v>0.4088</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -3556,24 +3574,25 @@
         <f>IF(AND(ISNUMBER(R40),ISNUMBER(M40),M40&lt;&gt;0),(R40-M40)/M40,"-")</f>
         <v/>
       </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T40" t="n">
+        <v>0.4282</v>
       </c>
       <c r="U40">
         <f>IF(AND(ISNUMBER(T40),ISNUMBER(N40),N40&lt;&gt;0),(T40-N40)/N40,"-")</f>
         <v/>
       </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V40" t="n">
+        <v>0.4812</v>
       </c>
       <c r="W40">
         <f>IF(AND(ISNUMBER(V40),ISNUMBER(O40),O40&lt;&gt;0),(V40-O40)/O40,"-")</f>
         <v/>
       </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>26Q2 Sasa 锌精矿含锌 4,812t=0.4812 万吨（+18% YoY：品位 2.73%/+9.6%）；H1=9,094t（+5%）；26Q1=H1−Q2=4,282t（推算注明）。FY26 指引 18-20kt。源：CAML H1 2026 运营更新（RNS 7/8）</t>
+        </is>
+      </c>
       <c r="Z40" t="inlineStr">
         <is>
           <t>锌精矿含锌量；自然年；季报（LSE）；铅目录同步建行；2026-08-18新增骨架行，数据待回填</t>
@@ -3681,16 +3700,21 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>未披露</t>
         </is>
       </c>
       <c r="W41">
         <f>IF(AND(ISNUMBER(V41),ISNUMBER(O41),O41&lt;&gt;0),(V41-O41)/O41,"-")</f>
         <v/>
       </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Hecla 2Q26(8/4)仅披露银/金金属量+精矿吨数（GC锌精矿17,990吨+LF锌精矿6,527吨），不再披露锌含金属量</t>
+        </is>
+      </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>锌精矿含锌量；自然年；季报（NYSE）≈季后3-4周；铅目录同步建行；2026-08-18新增骨架行，数据待回填</t>
+          <t>锌精矿含锌量；自然年；季报（NYSE）≈季后3-4周；铅目录同步建行；2026-08-18新增骨架行，数据待回填；源：Hecla 2Q26 业绩新闻稿（8-K ex99.1）；含金属量口径缺官方值</t>
         </is>
       </c>
     </row>
@@ -3795,13 +3819,18 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>H1=6.3906</t>
         </is>
       </c>
       <c r="W42">
         <f>IF(AND(ISNUMBER(V42),ISNUMBER(O42),O42&lt;&gt;0),(V42-O42)/O42,"-")</f>
         <v/>
       </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中报（7/30）：H1 矿产锌 63,906 吨=6.3906 万吨（半年口径，未拆季）。源：西部矿业 2026 半年度报告（巨潮 1225446414）</t>
+        </is>
+      </c>
       <c r="Z42" t="inlineStr">
         <is>
           <t>跨品种修正：原仅铅目录；A股年报+中报披露（季报无产量）；2026-08-18新增骨架行，数据待回填</t>
@@ -3909,13 +3938,18 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>待发布</t>
         </is>
       </c>
       <c r="W43">
         <f>IF(AND(ISNUMBER(V43),ISNUMBER(O43),O43&lt;&gt;0),(V43-O43)/O43,"-")</f>
         <v/>
       </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>华钰矿业中报 8 月底前窗口 → 待发布（截至 2026-08-25 未见披露）</t>
+        </is>
+      </c>
       <c r="Z43" t="inlineStr">
         <is>
           <t>跨品种修正：原仅铅目录；A股年报+中报披露（季报无产量）；2026-08-18新增骨架行，数据待回填</t>
@@ -4115,7 +4149,7 @@
         <v>145.8053</v>
       </c>
       <c r="V47" t="n">
-        <v>109.2542</v>
+        <v>116.126</v>
       </c>
     </row>
   </sheetData>
@@ -4441,6 +4475,11 @@
         <f>IF(AND(ISNUMBER(V3),ISNUMBER(O3),O3&lt;&gt;0),(V3-O3)/O3,"-")</f>
         <v/>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>日财年止3月，日26Q2=FY2027Q1；Q1决算仅披露锌部门营收526亿日元(同比-17.4%，LME锌价下跌)，无季度精炼锌产量吨数(仅半年度披露产量计划) → 公开渠道无法获取。来源:三井金属FY27 Q1决算(TDnet,约8/7)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4515,7 +4554,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Q2 2026财报已发布（Revenue 6.37T KRW/OP 587B KRW），精炼锌产量数据待补充</t>
+          <t>Q2 2026财报已发布(营收6.37万亿韩元/营业利润5870亿韩元创纪录，白银销量约+3倍)；但公司仅披露年度锌锭销量(2025=59.07万吨/2026计划60万吨)，季度报告/IR均为财务口径，无分季度精炼锌产量吨数 → 公开渠道无法获取。来源:Korea Zinc 2Q26业绩(Yonhap 8/5)+DART季报(8/13)+SMM</t>
         </is>
       </c>
     </row>
@@ -4828,13 +4867,16 @@
         <f>IF(AND(ISNUMBER(T8),ISNUMBER(N8),N8&lt;&gt;0),(T8-N8)/N8,"-")</f>
         <v/>
       </c>
+      <c r="V8" t="n">
+        <v>3.5532</v>
+      </c>
       <c r="W8">
         <f>IF(AND(ISNUMBER(V8),ISNUMBER(O8),O8&lt;&gt;0),(V8-O8)/O8,"-")</f>
         <v/>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>产量恢复</t>
+          <t>26Q2=3.5532万吨(35,532吨)同比-33.9%(年度计划检修+复产延迟+检修前额外停车，一次性扰动非趋势减产)/H1=8.3658万吨。来源:penoles.com.mx Informe_Director_2T26_Eng.pdf(2026-08-04)</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -5078,7 +5120,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>KZ产能分配至SMC</t>
+          <t>公开渠道无法获取分季度精炼锌产量。口径提示:SMC=Sun Metals Corporation(Korea Zinc 100%澳洲子公司Townsville，非韩国本土第二大冶炼厂)，非上市私人子公司不披露季度产量，集团亦不按分厂披露。来源:Korea Zinc IR/DART+Sun Metals官网+AFR</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -5292,7 +5334,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>未披露</t>
         </is>
       </c>
       <c r="W14">
@@ -5301,7 +5343,12 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>跨品种修正：原仅铅目录（精炼铅）；A股年报+中报披露；2026-08-18新增骨架行，数据待回填</t>
+          <t>株冶集团2026中报仅财务口径（营收141.5亿+35.9%/净利19.5亿+232.7%），未披露锌锭产量吨数（仅相对表述"析出锌超时序进度0.64%"）</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>源：株冶集团2026年半年度报告（SSE）；产能锚点68万吨锌产品</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5453,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>待发布</t>
         </is>
       </c>
       <c r="W15">
@@ -5415,7 +5462,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>跨品种修正：原仅铅目录（精炼铅）；A股年报+中报披露；2026-08-18新增骨架行，数据待回填</t>
+          <t>锌业股份中报 8 月底前窗口 → 待发布（截至 2026-08-25 未见披露）</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6483,6 +6530,57 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>锌 26Q2 欠账公司补录（紫金/Peñoles/Sibanye/KAZ/PanAm/Adriatic/Silvercorp/CAM/Hecla/西部矿业/华钰/株冶/锌业/KoreaZinc/SMC/Mitsui/Torreon）</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>各公司官方IR/财报 + SMM快讯 + 新浪海外锌矿Q2追踪（详见各行动因列）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>锌批A：Silvercorp 26Q2=0.1996万吨(6-K)；Hecla→未披露(仅精矿吨数)；株冶冶炼→未披露(中报仅财务口径)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Silvercorp 6-K 7/15；Hecla 8-K ex99.1 8/4；株冶2026中报</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>锌 26Q2 批B：KAZ 1.13/PanAm 1.56/CAML 0.4812/西部矿业 H1=6.3906；Sibanye·DPM·华钰·锌业 待发布/待拆</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>KAZ 官网（8/11）；PanAm（8/12）；CAML RNS（7/8）；西部矿业中报；DPM（7/30）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel/锌.xlsx
+++ b/excel/锌.xlsx
@@ -2264,13 +2264,18 @@
         <f>IF(AND(ISNUMBER(T19),ISNUMBER(N19),N19&lt;&gt;0),(T19-N19)/N19,"-")</f>
         <v/>
       </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="W19">
         <f>IF(AND(ISNUMBER(V19),ISNUMBER(O19),O19&lt;&gt;0),(V19-O19)/O19,"-")</f>
         <v/>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>选矿产设备维修</t>
+          <t>私有化后无公开披露：Polymetal 2024/3/7出售全部俄罗斯资产后更名Solidcore（仅剩哈萨克资产，26Q2季报2026/9/9才发布且不含Ozernoye）；俄资产无公开季度产量（2026-08-31核：akm.ru + solidcore-resources.com）</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2441,13 +2446,23 @@
         <f>IF(AND(ISNUMBER(T21),ISNUMBER(N21),N21&lt;&gt;0),(T21-N21)/N21,"-")</f>
         <v/>
       </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="W21">
         <f>IF(AND(ISNUMBER(V21),ISNUMBER(O21),O21&lt;&gt;0),(V21-O21)/O21,"-")</f>
         <v/>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>明确被列为减产矿山</t>
+          <t>South32 FY26 Q4季报（2026-07-20，Investegate全文核对）锌资产仅Cannington(澳)+Hermosa Taylor(美,在建)，无任何墨西哥/Capela资产披露，26Q2无数可填</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>归属存疑（2026-08-31核）：South32资产组合中无墨西哥锌矿，「墨西哥Capela等」挂South32名下疑为历史错位；未擅自改历史行归属，26Q2标-</t>
         </is>
       </c>
     </row>
@@ -2568,13 +2583,16 @@
         <f>IF(AND(ISNUMBER(T23),ISNUMBER(N23),N23&lt;&gt;0),(T23-N23)/N23,"-")</f>
         <v/>
       </c>
+      <c r="V23" t="n">
+        <v>9.241300000000001</v>
+      </c>
       <c r="W23">
         <f>IF(AND(ISNUMBER(V23),ISNUMBER(O23),O23&lt;&gt;0),(V23-O23)/O23,"-")</f>
         <v/>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>官方季报口径（矿山产锌）；26Q1同比-4.2%；注意券商跟踪表25Q4=12.89/全年40.00为锌+铅口径，官方年报矿产锌35.75万吨，勿混用</t>
+          <t>中报累计相减推算：2026H1矿山产锌（锌精矿含锌）176,922吨（同比-1.5%，中报全文p11）−26Q1官方季报84,509吨=92,413吨（26Q2，同比+1.1%）；摘要「矿产锌(铅)20万吨」为锌+铅合计口径未采用。来源：cninfo紫金2026半年报（2026-08-22，1225493590.PDF）</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -4785,18 +4803,21 @@
         <f>IF(AND(ISNUMBER(T7),ISNUMBER(N7),N7&lt;&gt;0),(T7-N7)/N7,"-")</f>
         <v/>
       </c>
+      <c r="V7" t="n">
+        <v>3.37</v>
+      </c>
       <c r="W7">
         <f>IF(AND(ISNUMBER(V7),ISNUMBER(O7),O7&lt;&gt;0),(V7-O7)/O7,"-")</f>
         <v/>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>氧化锌产出增加</t>
+          <t>Nexa 2Q26报告分厂表：锌金属产量33.7kt（同比+18.2%/环比-7.2%）；口径=锌金属（不含氧化锌9.1kt），与历史行一致。来源：SEC 6-K ex99-1（2026-08-05）</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>26Q2 Nexa冶炼锌金属+氧化合计125kt(-10%)；分冶炼厂数据未单独披露，待补充</t>
+          <t>26Q2已入库：Nexa 2Q26起分厂表披露（此前8/23注「分厂未披露」已被证伪，以分厂表为准）</t>
         </is>
       </c>
     </row>
@@ -5032,18 +5053,21 @@
         <f>IF(AND(ISNUMBER(T10),ISNUMBER(N10),N10&lt;&gt;0),(T10-N10)/N10,"-")</f>
         <v/>
       </c>
+      <c r="V10" t="n">
+        <v>6.2</v>
+      </c>
       <c r="W10">
         <f>IF(AND(ISNUMBER(V10),ISNUMBER(O10),O10&lt;&gt;0),(V10-O10)/O10,"-")</f>
         <v/>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Q2 2026财报已发布，分冶炼厂产量数据待补充</t>
+          <t>Nexa 2Q26报告分厂表：锌金属62.0kt（同比-26.1%/环比-27.4%）；5月火灾致铸造车间停产（估计影响约7kt），6月恢复正常，受影响量预计2H26补回，全年销量指引维持。来源：SEC 6-K ex99-1（2026-08-05）</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>26Q2 Nexa冶炼锌金属+氧化合计125kt(-10%)；分冶炼厂数据未单独披露，待补充</t>
+          <t>26Q2已入库：Nexa 2Q26分厂表（此前8/23注「分厂未披露」已被证伪）</t>
         </is>
       </c>
     </row>
@@ -5114,18 +5138,23 @@
         <f>IF(AND(ISNUMBER(T11),ISNUMBER(N11),N11&lt;&gt;0),(T11-N11)/N11,"-")</f>
         <v/>
       </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="W11">
         <f>IF(AND(ISNUMBER(V11),ISNUMBER(O11),O11&lt;&gt;0),(V11-O11)/O11,"-")</f>
         <v/>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>公开渠道无法获取分季度精炼锌产量。口径提示:SMC=Sun Metals Corporation(Korea Zinc 100%澳洲子公司Townsville，非韩国本土第二大冶炼厂)，非上市私人子公司不披露季度产量，集团亦不按分厂披露。来源:Korea Zinc IR/DART+Sun Metals官网+AFR</t>
+          <t>公开渠道无法获取分季度精炼锌产量。口径提示:SMC=Sun Metals Corporation(Korea Zinc 100%澳洲子公司Townsville，非韩国本土第二大冶炼厂)，非上市私人子公司不披露季度产量，集团亦不按分厂披露。来源:Korea Zinc IR/DART+Sun Metals官网+AFR｜2026-08-31核：Korea Zinc 2Q26 IR（2026-08-06）SMC章节仅披露营收/利润（销售$299.0M、OP $7.9M），未再披露分季锌产量（25Q2及之前曾披露，25Q2=65,546t），26Q2标-；报告称物流正常化后产量已恢复</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>26Q2 Nexa冶炼锌金属+氧化合计125kt(-10%)；分冶炼厂数据未单独披露，待补充</t>
+          <t>26Q2=-：Korea Zinc 2Q26 IR未披露SMC锌产量（此前8/23误贴Nexa 125kt注，已更正）</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6581,6 +6610,23 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>锌 26Q2 欠账收口：紫金9.2413（中报H1矿山产锌176,922t−Q1官方84,509t推算）；Três Marias 3.37/Cajamarquilla 6.20（Nexa 2Q26分厂表，后者5月火灾-26%）；Polymetal/South32-Capela/SMC 标-（私有化无披露/South32季报无该资产·归属存疑/Korea Zinc 2Q26 IR起不再披露分厂产量）</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>紫金2026半年报cninfo 1225493590（8/22）；Nexa 2Q26 SEC 6-K ex99-1（8/5）；South32 June2026季报（7/20 Investegate）；Korea Zinc 2Q26 IR（8/6）；akm.ru/Solidcore官网</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel/锌.xlsx
+++ b/excel/锌.xlsx
@@ -4489,13 +4489,16 @@
         <f>IF(AND(ISNUMBER(T3),ISNUMBER(N3),N3&lt;&gt;0),(T3-N3)/N3,"-")</f>
         <v/>
       </c>
+      <c r="V3" t="n">
+        <v>4.5</v>
+      </c>
       <c r="W3">
         <f>IF(AND(ISNUMBER(V3),ISNUMBER(O3),O3&lt;&gt;0),(V3-O3)/O3,"-")</f>
         <v/>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>日财年止3月，日26Q2=FY2027Q1；Q1决算仅披露锌部门营收526亿日元(同比-17.4%，LME锌价下跌)，无季度精炼锌产量吨数(仅半年度披露产量计划) → 公开渠道无法获取。来源:三井金属FY27 Q1决算(TDnet,约8/7)</t>
+          <t>三井金属FY27/3期Q1(2026.4-6)决算说明资料(8/7)：亜鉛生産量45千t=4.5万吨(短信仅财务口径,产量在说明资料)；通期计划218千t(8/7修正)</t>
         </is>
       </c>
     </row>
@@ -4566,13 +4569,18 @@
         <f>IF(AND(ISNUMBER(T4),ISNUMBER(N4),N4&lt;&gt;0),(T4-N4)/N4,"-")</f>
         <v/>
       </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>未披露</t>
+        </is>
+      </c>
       <c r="W4">
         <f>IF(AND(ISNUMBER(V4),ISNUMBER(O4),O4&lt;&gt;0),(V4-O4)/O4,"-")</f>
         <v/>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Q2 2026财报已发布(营收6.37万亿韩元/营业利润5870亿韩元创纪录，白银销量约+3倍)；但公司仅披露年度锌锭销量(2025=59.07万吨/2026计划60万吨)，季度报告/IR均为财务口径，无分季度精炼锌产量吨数 → 公开渠道无法获取。来源:Korea Zinc 2Q26业绩(Yonhap 8/5)+DART季报(8/13)+SMM</t>
+          <t>Korea Zinc Q2财报(8/6)仅披露锌销量146,374MT(standalone,-2.8%YoY)；产量年度才披露(2025年600,006MT)</t>
         </is>
       </c>
     </row>
@@ -6126,7 +6134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6627,6 +6635,23 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>锌锭 26Q2 回填：Mitsui Mining 4.5（三井金属FY27/3 Q1决算说明资料45kt）；Korea Zinc=未披露（Q2财报仅销量146,374MT）</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>三井金属决算说明资料 8/7；Korea Zinc IR Earnings Release 8/6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel/锌.xlsx
+++ b/excel/锌.xlsx
@@ -2933,10 +2933,8 @@
         <f>IF(AND(ISNUMBER(T29),ISNUMBER(N29),N29&lt;&gt;0),(T29-N29)/N29,"-")</f>
         <v/>
       </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>待发布</t>
-        </is>
+      <c r="V29" t="n">
+        <v>2.5</v>
       </c>
       <c r="W29">
         <f>IF(AND(ISNUMBER(V29),ISNUMBER(O29),O29&lt;&gt;0),(V29-O29)/O29,"-")</f>
@@ -2944,7 +2942,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Sibanye H1 2026（JSE，约 8/28）待发布；FY2025 Century 应付锌 101kt（+22% 超指引上限 97.8kt）。源：Sibanye 2025 年报（2/20）</t>
+          <t>26Q2=2.5万吨（推导值：H1 2026 Century应付锌45kt[8/27经营更新] − 26Q1 20kt[已披露] = 25kt；Q2单季未直接披露，9/1正式中报后复核）。FY2025 Century应付锌101kt(+22%超指引上限97.8kt)。源：Sibanye 8/27经营更新 + 2025年报(2/20)</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3170,10 +3168,8 @@
         <f>IF(AND(ISNUMBER(T33),ISNUMBER(N33),N33&lt;&gt;0),(T33-N33)/N33,"-")</f>
         <v/>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>已发布待拆</t>
-        </is>
+      <c r="V33" t="n">
+        <v>0.6486</v>
       </c>
       <c r="W33">
         <f>IF(AND(ISNUMBER(V33),ISNUMBER(O33),O33&lt;&gt;0),(V33-O33)/O33,"-")</f>
@@ -3181,7 +3177,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>DPM Metals Q2 2026（7/30）已发，Vareš 宣布商产、年底满产；锌分矿明细待拆 → 暂记。源：dpmmetals.com 7/30</t>
+          <t>DPM Metals Q2 2026(7/30)：Vareš精矿含锌Q2=14.3Mlbs=0.6486万吨，直接披露；H1=24.3Mlbs，勾稽Q1=10.0Mlbs=0.4536万吨✓（与26Q1格一致）；应付锌销量Q2=8.8Mlbs滞后于产量（交付时点）；Vareš已宣布商产，年底达85万吨/年矿石处理速率。源：dpmmetals.com 7/30季报</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3718,7 +3714,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>未披露</t>
+          <t>-</t>
         </is>
       </c>
       <c r="W41">
@@ -3826,19 +3822,15 @@
         <f>IF(AND(ISNUMBER(R42),ISNUMBER(M42),M42&lt;&gt;0),(R42-M42)/M42,"-")</f>
         <v/>
       </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T42" t="n">
+        <v>3.1953</v>
       </c>
       <c r="U42">
         <f>IF(AND(ISNUMBER(T42),ISNUMBER(N42),N42&lt;&gt;0),(T42-N42)/N42,"-")</f>
         <v/>
       </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>H1=6.3906</t>
-        </is>
+      <c r="V42" t="n">
+        <v>3.1953</v>
       </c>
       <c r="W42">
         <f>IF(AND(ISNUMBER(V42),ISNUMBER(O42),O42&lt;&gt;0),(V42-O42)/O42,"-")</f>
@@ -3851,7 +3843,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>跨品种修正：原仅铅目录；A股年报+中报披露（季报无产量）；2026-08-18新增骨架行，数据待回填</t>
+          <t>跨品种修正：原仅铅目录；A股年报+中报披露（季报无产量）；2026-08-18新增骨架行，数据待回填；中报H1矿产锌6.3906万吨，Q1未披露，两季平分拟合</t>
         </is>
       </c>
     </row>
@@ -3954,10 +3946,8 @@
         <f>IF(AND(ISNUMBER(T43),ISNUMBER(N43),N43&lt;&gt;0),(T43-N43)/N43,"-")</f>
         <v/>
       </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>待发布</t>
-        </is>
+      <c r="V43" t="n">
+        <v>0.3213</v>
       </c>
       <c r="W43">
         <f>IF(AND(ISNUMBER(V43),ISNUMBER(O43),O43&lt;&gt;0),(V43-O43)/O43,"-")</f>
@@ -3965,7 +3955,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>华钰矿业中报 8 月底前窗口 → 待发布（截至 2026-08-25 未见披露）</t>
+          <t>26Q2单季锌精矿产量3,212.51金属吨=0.3213万吨（经营公告直接披露口径）；26Q1未披露保持'-'（A股季报不披露产量）</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
@@ -4571,7 +4561,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>未披露</t>
+          <t>-</t>
         </is>
       </c>
       <c r="W4">
@@ -5371,7 +5361,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>未披露</t>
+          <t>-</t>
         </is>
       </c>
       <c r="W14">
@@ -5479,19 +5469,15 @@
         <f>IF(AND(ISNUMBER(R15),ISNUMBER(M15),M15&lt;&gt;0),(R15-M15)/M15,"-")</f>
         <v/>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T15" t="n">
+        <v>6.265</v>
       </c>
       <c r="U15">
         <f>IF(AND(ISNUMBER(T15),ISNUMBER(N15),N15&lt;&gt;0),(T15-N15)/N15,"-")</f>
         <v/>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>待发布</t>
-        </is>
+      <c r="V15" t="n">
+        <v>6.265</v>
       </c>
       <c r="W15">
         <f>IF(AND(ISNUMBER(V15),ISNUMBER(O15),O15&lt;&gt;0),(V15-O15)/O15,"-")</f>
@@ -5499,7 +5485,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>锌业股份中报 8 月底前窗口 → 待发布（截至 2026-08-25 未见披露）</t>
+          <t>锌业股份H1 2026锌金属产品12.53万吨（安泰科口径，约占国内4%）；26Q1未披露，26Q1=26Q2=12.53/2=6.265万吨（H1/2拟合，中报无分季拆分）</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6652,6 +6638,23 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>26Q2 文本格规整：西部矿业 H1=6.3906→Q1/Q2 各 3.1953（平分拟合）；Hecla/Korea Zinc/中国(未披露)→'-'（已核实无季度数据）</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>西部矿业中报 7/30；Hecla 2Q26 财报 8/4；Korea Zinc IR 8/6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
